--- a/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
+++ b/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
@@ -1,41 +1,142 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\els_janssens\CORE\Rule_Authoring\core-contributor\rules\NEW-RULE\negative\02\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC36EC89-70EA-4014-9904-30259240A964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="Validation" sheetId="3" r:id="rId3"/>
     <sheet name="cm.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>cm.xpt</t>
+  </si>
+  <si>
+    <t>Concomitant and Prior Medications</t>
+  </si>
+  <si>
+    <t>Error group</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>Error level</t>
+  </si>
+  <si>
+    <t>Row num</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Error value</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>define_variable_origin_type</t>
+  </si>
+  <si>
+    <t>variable_name</t>
+  </si>
+  <si>
+    <t>CMTRT</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>CMSEQ</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Reported Name of Drug, Med, or Therapy</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>ABC-001</t>
+  </si>
+  <si>
+    <t>Ibuprofen</t>
+  </si>
+  <si>
+    <t>Paracetamol</t>
+  </si>
+  <si>
+    <t>define_variable_source_type</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -50,37 +151,25 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <i/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -89,21 +178,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -428,254 +524,276 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Version</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <v>3-4</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Label</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="str">
-        <v>cm.xpt</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <v>Concomitant and Prior Medications</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="29.85546875" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Error group</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Sheet</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>Error level</v>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v>Row num</v>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v>Variable</v>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v>Error value</v>
-      </c>
-    </row>
-    <row r="2" xml:space="preserve">
-      <c r="A2" s="3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="str">
-        <v>cm.xpt</v>
-      </c>
-      <c r="C2" s="3" t="str">
-        <v>Dataset</v>
-      </c>
-      <c r="D2" s="3" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="E2" s="3" t="str">
-        <v>define_variable_origin_type</v>
-      </c>
-      <c r="F2" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">
-</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3">
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="str">
-        <v>cm.xpt</v>
-      </c>
-      <c r="C3" s="3" t="str">
-        <v>Dataset</v>
-      </c>
-      <c r="D3" s="3" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="E3" s="3" t="str">
-        <v>variable_name</v>
-      </c>
-      <c r="F3" s="3" t="str">
-        <v>CMTRT</v>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>USUBJID</v>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v>CMSEQ</v>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v>CMTRT</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="4" t="str">
-        <v>Unique Subject Identifier</v>
-      </c>
-      <c r="D2" s="4" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="E2" s="4" t="str">
-        <v>Reported Name of Drug, Med, or Therapy</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="4" t="str">
-        <v>Num</v>
-      </c>
-      <c r="E3" s="4" t="str">
-        <v>Char</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>10</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>14</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <v>8</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="str">
-        <v>ABC</v>
-      </c>
-      <c r="B5" s="3" t="str">
-        <v>CM</v>
-      </c>
-      <c r="C5" s="3" t="str">
-        <v>ABC-001</v>
-      </c>
-      <c r="D5" s="3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="str">
-        <v>Ibuprofen</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="str">
-        <v>ABC</v>
-      </c>
-      <c r="B6" s="3" t="str">
-        <v>CM</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <v>ABC-001</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="E5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="E6" s="3" t="str">
-        <v>Paracetamol</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="str">
-        <v>ABC</v>
-      </c>
-      <c r="B7" s="3" t="str">
-        <v>CM</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <v>ABC-001</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="E6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError sqref="A1:E7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
+++ b/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/negative/02/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490C9158-5096-5943-86A7-0BE192FFFDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFFA562-E96E-5840-9CDC-094CD2966A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="93">
   <si>
     <t>Product</t>
   </si>
@@ -77,9 +77,6 @@
     <t>define_dataset_key_sequence</t>
   </si>
   <si>
-    <t>STUDYID,USUBJID,AEDECOD</t>
-  </si>
-  <si>
     <t>define_key_sequence_is_unique</t>
   </si>
   <si>
@@ -300,6 +297,12 @@
   </si>
   <si>
     <t>HEAD PAIN</t>
+  </si>
+  <si>
+    <t>STUDYID,USUBJID,AEDECOD,AETRTEM</t>
+  </si>
+  <si>
+    <t>STUDYID,RDOMAIN,USUBJID,IDVAR,IDVARVAL,QNAM</t>
   </si>
 </sst>
 </file>
@@ -719,9 +722,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,7 +732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -748,9 +751,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -758,7 +761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -766,7 +769,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -784,10 +787,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -807,7 +810,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -823,11 +826,11 @@
       <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="F2" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -841,13 +844,13 @@
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -863,11 +866,11 @@
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="F4" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -881,13 +884,13 @@
         <v>6</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -903,11 +906,11 @@
       <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="F6" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -921,16 +924,97 @@
         <v>7</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>19</v>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="6">
+        <v>5</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="6">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="6">
+        <v>6</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="6">
+        <v>6</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F7" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1 A3:F3 A2:E2 A5:F5 A4:E4 A7:F7 A6:E6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -938,123 +1022,123 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>50</v>
       </c>
@@ -1092,232 +1176,232 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="E6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L6" s="1" t="s">
+      <c r="H7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C10" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1332,101 +1416,101 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="4">
         <v>14</v>
@@ -1435,109 +1519,109 @@
         <v>10</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C5" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C6" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="I6" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="F7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>

--- a/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
+++ b/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/negative/02/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF390B67-0F2E-A340-BBCA-6091A9CA55FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8339151-44BC-5340-B7E7-2CD684AF5368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1420" yWindow="680" windowWidth="28800" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="276">
   <si>
     <t>Product</t>
   </si>
@@ -834,13 +834,31 @@
   </si>
   <si>
     <t>Trial Summary Parameters</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>TA</t>
+  </si>
+  <si>
+    <t>[ABSENT]</t>
+  </si>
+  <si>
+    <t>TE</t>
+  </si>
+  <si>
+    <t>TI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -859,6 +877,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -902,7 +927,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -916,6 +941,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1278,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -1299,6 +1325,206 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="7">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E7" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D8" t="s">
+        <v>271</v>
+      </c>
+      <c r="E8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>270</v>
+      </c>
+      <c r="D9" t="s">
+        <v>271</v>
+      </c>
+      <c r="E9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
+        <v>2</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
+++ b/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
@@ -37,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -60,13 +60,8 @@
       <name val="Calibri"/>
       <i/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -74,12 +69,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -109,14 +98,13 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -626,7 +614,7 @@
         <v>N/A</v>
       </c>
       <c r="E6" s="3" t="str">
-        <v>$max_data_length</v>
+        <v>$max_variable_value_length</v>
       </c>
       <c r="F6" s="3">
         <v>2</v>
@@ -646,7 +634,7 @@
         <v>N/A</v>
       </c>
       <c r="E7" s="3" t="str">
-        <v>$global_min_length</v>
+        <v>$global_min_variable_length</v>
       </c>
       <c r="F7" s="3">
         <v>3</v>
@@ -666,7 +654,7 @@
         <v>N/A</v>
       </c>
       <c r="E8" s="3" t="str">
-        <v>$global_max_length</v>
+        <v>$global_max_variable_length</v>
       </c>
       <c r="F8" s="3">
         <v>3</v>
@@ -740,98 +728,98 @@
       <c r="F2" s="5" t="str">
         <v>Visit Name</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Epoch</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="5" t="str">
         <v>Start Date/Time of Visit</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="5" t="str">
         <v>End Date/Time of Visit</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="5" t="str">
         <v>Study Day of Start of Visit</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="5" t="str">
         <v>Study Day of End of Visit</v>
       </c>
-      <c r="L2" s="6" t="str">
+      <c r="L2" s="5" t="str">
         <v>Description of Unplanned Visit</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="K3" s="6" t="str">
+      <c r="K3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="L3" s="6" t="str">
+      <c r="L3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>3</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
         <v>9</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>9</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>3</v>
       </c>
-      <c r="K4" s="6">
-        <v>1</v>
-      </c>
-      <c r="L4" s="6">
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
         <v>9</v>
       </c>
     </row>
@@ -908,71 +896,71 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="5" t="str">
         <v>Visit Number</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Visit Name</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Visit Start Rule</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Visit End Rule</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>3</v>
       </c>
-      <c r="C4" s="6">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
         <v>9</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>8</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>9</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
+++ b/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/negative/02/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A1A657-6DE3-9741-B5FE-5C2576D73D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED25880-78D6-3141-947F-691CA25669E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="186">
   <si>
     <t>Product</t>
   </si>
@@ -696,7 +696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -726,13 +726,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1095,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0174FA04-2535-614A-BAD8-EA941C362AF5}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="17" customWidth="1"/>
@@ -1137,7 +1130,7 @@
       <c r="E2" t="s">
         <v>118</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="9" t="s">
         <v>178</v>
       </c>
     </row>
@@ -1157,11 +1150,10 @@
       <c r="E3" t="s">
         <v>117</v>
       </c>
-      <c r="F3" s="14"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
         <v>175</v>
@@ -1170,13 +1162,13 @@
         <v>185</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>177</v>
+        <v>101</v>
+      </c>
+      <c r="F4" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1193,7 +1185,47 @@
         <v>9</v>
       </c>
       <c r="E5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -2198,7 +2230,7 @@
       <c r="D6" s="4">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="10" t="s">
         <v>154</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -2436,7 +2468,7 @@
       <c r="D9" s="4">
         <v>5</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="10" t="s">
         <v>165</v>
       </c>
       <c r="F9" s="4" t="s">

--- a/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
+++ b/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/negative/02/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/negative/02/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8339151-44BC-5340-B7E7-2CD684AF5368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F2E607-F602-BA4E-8A6C-B04C9C8832FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-8560" windowWidth="51200" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="274">
   <si>
     <t>Product</t>
   </si>
@@ -842,16 +842,10 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>TA</t>
-  </si>
-  <si>
-    <t>[ABSENT]</t>
-  </si>
-  <si>
-    <t>TE</t>
-  </si>
-  <si>
-    <t>TI</t>
+    <t>$missing_trial_design_domains</t>
+  </si>
+  <si>
+    <t>"TM", "TI", "TD", "TA"</t>
   </si>
 </sst>
 </file>
@@ -927,7 +921,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -942,6 +936,9 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1348,184 +1345,34 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E3" t="s">
-        <v>274</v>
-      </c>
-      <c r="F3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>268</v>
-      </c>
-      <c r="C4" t="s">
-        <v>270</v>
-      </c>
-      <c r="D4" t="s">
-        <v>271</v>
-      </c>
-      <c r="E4" t="s">
-        <v>275</v>
-      </c>
-      <c r="F4" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C5" t="s">
-        <v>270</v>
-      </c>
-      <c r="D5" t="s">
-        <v>271</v>
-      </c>
-      <c r="E5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" t="s">
-        <v>268</v>
-      </c>
+      <c r="F3" s="8"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="7">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="A6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D7" t="s">
-        <v>271</v>
-      </c>
-      <c r="E7" t="s">
-        <v>272</v>
-      </c>
-      <c r="F7" t="s">
-        <v>273</v>
-      </c>
+      <c r="B7" s="7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>270</v>
-      </c>
-      <c r="D8" t="s">
-        <v>271</v>
-      </c>
-      <c r="E8" t="s">
-        <v>274</v>
-      </c>
-      <c r="F8" t="s">
-        <v>273</v>
-      </c>
+      <c r="B8" s="7"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>270</v>
-      </c>
-      <c r="D9" t="s">
-        <v>271</v>
-      </c>
-      <c r="E9" t="s">
-        <v>275</v>
-      </c>
-      <c r="F9" t="s">
-        <v>273</v>
-      </c>
+      <c r="B9" s="7"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>270</v>
-      </c>
-      <c r="D10" t="s">
-        <v>271</v>
-      </c>
-      <c r="E10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" t="s">
-        <v>268</v>
-      </c>
+      <c r="B10" s="7"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="7">
-        <v>2</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
+++ b/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/negative/02/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/negative/02/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F2E607-F602-BA4E-8A6C-B04C9C8832FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4FAEA4-C77C-8C46-BEBF-AAE6D0F07AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-8560" windowWidth="51200" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-7000" windowWidth="51200" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -845,7 +845,7 @@
     <t>$missing_trial_design_domains</t>
   </si>
   <si>
-    <t>"TM", "TI", "TD", "TA"</t>
+    <t>"TM", "TI", "TE", "TD", "TA"</t>
   </si>
 </sst>
 </file>

--- a/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
+++ b/rules/NEW-RULE/negative/02/data/new-rule-negative-02.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -63,12 +63,8 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -82,12 +78,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,7 +107,7 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -125,7 +115,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -590,7 +579,7 @@
         <v>$define_loinc_version</v>
       </c>
       <c r="F4" s="3">
-        <v>9.99</v>
+        <v>2.83</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +974,7 @@
       <c r="X5" s="3">
         <v>-7</v>
       </c>
-      <c r="Y5" s="7" t="str">
+      <c r="Y5" s="6" t="str">
         <v>100001-7</v>
       </c>
     </row>
